--- a/table4.xlsx
+++ b/table4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{853255F3-3F80-4CED-99AB-0A7128C414C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA0F142-C9CF-480E-9FE6-F67CF3A13A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>교시</t>
   </si>
@@ -66,20 +66,385 @@
     <t>7(15:00)</t>
   </si>
   <si>
-    <t>8(16:00)</t>
-  </si>
-  <si>
-    <t>윤사</t>
-  </si>
-  <si>
     <t>창진</t>
+  </si>
+  <si>
+    <t>체육A</t>
+  </si>
+  <si>
+    <t>공영B</t>
+  </si>
+  <si>
+    <t>공수2</t>
+  </si>
+  <si>
+    <t>공국B</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>윤승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>희</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유승희</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김남</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>훈</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공영A</t>
+  </si>
+  <si>
+    <t>통사2</t>
+  </si>
+  <si>
+    <t>통과C</t>
+  </si>
+  <si>
+    <t>한국2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혜</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김효</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공국A</t>
+  </si>
+  <si>
+    <t>한자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장환준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>체육B</t>
+  </si>
+  <si>
+    <t>통과D</t>
+  </si>
+  <si>
+    <t>통과A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헌</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>박소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>희</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안재익</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주석준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>과실2</t>
+  </si>
+  <si>
+    <t>동아리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미술</t>
+  </si>
+  <si>
+    <t>통과B</t>
+  </si>
+  <si>
+    <t>권혜민</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>훈</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +465,20 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -187,10 +566,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -199,10 +578,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,207 +925,272 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>308</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="2">
-        <v>202</v>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="3" t="s">
-        <v>15</v>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>308</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="2">
-        <v>203</v>
-      </c>
-      <c r="D6" s="2">
-        <v>205</v>
-      </c>
-      <c r="E6" s="2">
-        <v>312</v>
-      </c>
-      <c r="F6" s="7"/>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8"/>
+      <c r="B7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="2">
-        <v>201</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="2">
-        <v>312</v>
-      </c>
-      <c r="F8" s="7"/>
+      <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8"/>
+      <c r="B9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2">
-        <v>304</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="2">
-        <v>309</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>304</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="2">
-        <v>309</v>
-      </c>
-      <c r="E12" s="2">
-        <v>204</v>
-      </c>
-      <c r="F12" s="7"/>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="F15" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="10">
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
